--- a/data/normalized/basidiospore_filled_v4.xlsx
+++ b/data/normalized/basidiospore_filled_v4.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hensley/Desktop/wiscam_microscopy/data/normalized/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79B3F29F-C494-A347-B704-4C6F6B1D4512}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EA10495-587A-0B48-952F-EA169ED7D938}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="680" windowWidth="29400" windowHeight="18440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,20 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="parse_log" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -1079,78 +1092,78 @@
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="B2" t="s">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="C2" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="D2">
         <v>25</v>
       </c>
       <c r="E2">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="F2">
+        <v>8</v>
+      </c>
+      <c r="G2">
+        <v>10</v>
+      </c>
+      <c r="H2">
+        <v>10</v>
+      </c>
+      <c r="I2">
+        <v>8</v>
+      </c>
+      <c r="J2">
         <v>8.5</v>
       </c>
-      <c r="G2">
-        <v>11.5</v>
-      </c>
-      <c r="H2">
-        <v>14.5</v>
-      </c>
-      <c r="I2">
-        <v>7</v>
-      </c>
-      <c r="J2">
-        <v>8</v>
-      </c>
       <c r="K2">
-        <v>11.5</v>
+        <v>9.5</v>
       </c>
       <c r="L2">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="M2" s="2">
-        <v>0.89</v>
+        <v>0.84210526315789469</v>
       </c>
       <c r="N2" s="2">
-        <v>1.0950696320018529</v>
+        <v>1.017132094943241</v>
       </c>
       <c r="O2" s="2">
-        <v>1.29</v>
+        <v>1.117647058823529</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="B3" t="s">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="C3" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="D3">
         <v>25</v>
       </c>
       <c r="E3">
+        <v>6</v>
+      </c>
+      <c r="F3">
         <v>8</v>
       </c>
-      <c r="F3">
-        <v>9</v>
-      </c>
       <c r="G3">
-        <v>11.5</v>
+        <v>9.5</v>
       </c>
       <c r="H3">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J3">
         <v>8</v>
@@ -1162,39 +1175,39 @@
         <v>10</v>
       </c>
       <c r="M3" s="2">
-        <v>1.0105263157894739</v>
+        <v>0.94117647058823528</v>
       </c>
       <c r="N3" s="2">
-        <v>1.1945087611067799</v>
+        <v>1.015154216914836</v>
       </c>
       <c r="O3" s="2">
-        <v>1.406976744186047</v>
+        <v>1.0666666666666671</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="B4" t="s">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="C4" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="D4">
         <v>25</v>
       </c>
       <c r="E4">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F4">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="G4">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="H4">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="I4">
         <v>6.5</v>
@@ -1206,268 +1219,169 @@
         <v>8</v>
       </c>
       <c r="L4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M4" s="2">
-        <v>0.83783783783783783</v>
+        <v>1.055555555555556</v>
       </c>
       <c r="N4" s="2">
-        <v>1.327240994376564</v>
+        <v>1.25742253968254</v>
       </c>
       <c r="O4" s="2">
-        <v>1.567567567567568</v>
+        <v>1.461538461538461</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>25</v>
+        <v>48</v>
       </c>
       <c r="B5" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="C5" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="D5">
         <v>25</v>
       </c>
       <c r="E5">
-        <v>7.5</v>
+        <v>10</v>
       </c>
       <c r="F5">
-        <v>8.5</v>
+        <v>10</v>
       </c>
       <c r="G5">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H5">
         <v>13</v>
       </c>
       <c r="I5">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J5">
-        <v>7</v>
+        <v>8.5</v>
       </c>
       <c r="K5">
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="L5">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="M5" s="2">
-        <v>1.0476190476190479</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="N5" s="2">
-        <v>1.211022792632205</v>
+        <v>1.283467877536979</v>
       </c>
       <c r="O5" s="2">
-        <v>1.4</v>
+        <v>1.4375</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="B6" t="s">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="C6" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="D6">
         <v>25</v>
       </c>
       <c r="E6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F6">
-        <v>9.5</v>
+        <v>10.5</v>
       </c>
       <c r="G6">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="H6">
         <v>12</v>
       </c>
       <c r="I6">
+        <v>7.5</v>
+      </c>
+      <c r="J6">
+        <v>7.5</v>
+      </c>
+      <c r="K6">
         <v>8.5</v>
       </c>
-      <c r="J6">
+      <c r="L6">
         <v>9</v>
       </c>
-      <c r="K6">
-        <v>10.5</v>
-      </c>
-      <c r="L6">
-        <v>11</v>
-      </c>
       <c r="M6" s="2">
-        <v>1</v>
+        <v>1.2352941176470591</v>
       </c>
       <c r="N6" s="2">
-        <v>1.1103157201381351</v>
+        <v>1.365101568627451</v>
       </c>
       <c r="O6" s="2">
-        <v>1.2777777777777779</v>
+        <v>1.533333333333333</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>29</v>
+        <v>68</v>
       </c>
       <c r="B7" t="s">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="C7" t="s">
-        <v>28</v>
-      </c>
-      <c r="D7">
-        <v>25</v>
-      </c>
-      <c r="E7">
-        <v>10</v>
-      </c>
-      <c r="F7">
-        <v>10.5</v>
-      </c>
-      <c r="G7">
-        <v>12</v>
-      </c>
-      <c r="H7">
-        <v>12.5</v>
-      </c>
-      <c r="I7">
-        <v>10</v>
-      </c>
-      <c r="J7">
-        <v>10.5</v>
-      </c>
-      <c r="K7">
-        <v>12</v>
-      </c>
-      <c r="L7">
-        <v>12.5</v>
-      </c>
-      <c r="M7" s="2">
-        <v>0.95238095238095233</v>
-      </c>
-      <c r="N7" s="2">
-        <v>1.004768966685488</v>
-      </c>
-      <c r="O7" s="2">
-        <v>1.1499999999999999</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="M7" s="2"/>
+      <c r="N7" s="2"/>
+      <c r="O7" s="2"/>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>31</v>
+        <v>69</v>
       </c>
       <c r="B8" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="C8" t="s">
-        <v>19</v>
-      </c>
-      <c r="D8">
-        <v>25</v>
-      </c>
-      <c r="E8">
-        <v>9</v>
-      </c>
-      <c r="F8">
-        <v>9</v>
-      </c>
-      <c r="G8">
-        <v>10.5</v>
-      </c>
-      <c r="H8">
-        <v>11.5</v>
-      </c>
-      <c r="I8">
-        <v>7.5</v>
-      </c>
-      <c r="J8">
-        <v>8.5</v>
-      </c>
-      <c r="K8">
-        <v>9.5</v>
-      </c>
-      <c r="L8">
-        <v>10</v>
-      </c>
-      <c r="M8" s="2">
-        <v>1</v>
-      </c>
-      <c r="N8" s="2">
-        <v>1.120581740626075</v>
-      </c>
-      <c r="O8" s="2">
-        <v>1.2666666666666671</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="M8" s="2"/>
+      <c r="N8" s="2"/>
+      <c r="O8" s="2"/>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>32</v>
+        <v>82</v>
       </c>
       <c r="B9" t="s">
-        <v>33</v>
+        <v>83</v>
       </c>
       <c r="C9" t="s">
-        <v>28</v>
-      </c>
-      <c r="D9">
-        <v>13</v>
-      </c>
-      <c r="E9">
-        <v>9.5</v>
-      </c>
-      <c r="F9">
-        <v>10</v>
-      </c>
-      <c r="G9">
-        <v>12</v>
-      </c>
-      <c r="H9">
-        <v>12</v>
-      </c>
-      <c r="I9">
-        <v>9.5</v>
-      </c>
-      <c r="J9">
-        <v>10</v>
-      </c>
-      <c r="K9">
-        <v>11.5</v>
-      </c>
-      <c r="L9">
-        <v>12.5</v>
-      </c>
-      <c r="M9" s="2">
-        <v>0.95238095238095233</v>
-      </c>
-      <c r="N9" s="2">
-        <v>1.0124446213779961</v>
-      </c>
-      <c r="O9" s="2">
-        <v>1.0909090909090911</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="M9" s="2"/>
+      <c r="N9" s="2"/>
+      <c r="O9" s="2"/>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>34</v>
+        <v>84</v>
       </c>
       <c r="B10" t="s">
-        <v>35</v>
+        <v>85</v>
       </c>
       <c r="C10" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="D10">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E10">
-        <v>7.5</v>
+        <v>9.5</v>
       </c>
       <c r="F10">
         <v>10</v>
@@ -1476,130 +1390,64 @@
         <v>11.5</v>
       </c>
       <c r="H10">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="I10">
+        <v>7.5</v>
+      </c>
+      <c r="J10">
         <v>8</v>
       </c>
-      <c r="J10">
+      <c r="K10">
         <v>9.5</v>
       </c>
-      <c r="K10">
-        <v>11.5</v>
-      </c>
       <c r="L10">
-        <v>12.5</v>
+        <v>9.5</v>
       </c>
       <c r="M10" s="2">
-        <v>0.9375</v>
+        <v>1.0526315789473679</v>
       </c>
       <c r="N10" s="2">
-        <v>1.0023546248229269</v>
+        <v>1.2309080018587919</v>
       </c>
       <c r="O10" s="2">
-        <v>1.0526315789473679</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>36</v>
+        <v>86</v>
       </c>
       <c r="B11" t="s">
-        <v>37</v>
+        <v>85</v>
       </c>
       <c r="C11" t="s">
         <v>38</v>
       </c>
-      <c r="D11">
-        <v>25</v>
-      </c>
-      <c r="E11">
-        <v>8</v>
-      </c>
-      <c r="F11">
-        <v>8</v>
-      </c>
-      <c r="G11">
-        <v>10</v>
-      </c>
-      <c r="H11">
-        <v>10</v>
-      </c>
-      <c r="I11">
-        <v>8</v>
-      </c>
-      <c r="J11">
-        <v>8.5</v>
-      </c>
-      <c r="K11">
-        <v>9.5</v>
-      </c>
-      <c r="L11">
-        <v>10</v>
-      </c>
-      <c r="M11" s="2">
-        <v>0.84210526315789469</v>
-      </c>
-      <c r="N11" s="2">
-        <v>1.017132094943241</v>
-      </c>
-      <c r="O11" s="2">
-        <v>1.117647058823529</v>
-      </c>
+      <c r="M11" s="2"/>
+      <c r="N11" s="2"/>
+      <c r="O11" s="2"/>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>39</v>
+        <v>87</v>
       </c>
       <c r="B12" t="s">
-        <v>37</v>
+        <v>85</v>
       </c>
       <c r="C12" t="s">
         <v>38</v>
       </c>
-      <c r="D12">
-        <v>25</v>
-      </c>
-      <c r="E12">
-        <v>6</v>
-      </c>
-      <c r="F12">
-        <v>8</v>
-      </c>
-      <c r="G12">
-        <v>9.5</v>
-      </c>
-      <c r="H12">
-        <v>10</v>
-      </c>
-      <c r="I12">
-        <v>6</v>
-      </c>
-      <c r="J12">
-        <v>8</v>
-      </c>
-      <c r="K12">
-        <v>9.5</v>
-      </c>
-      <c r="L12">
-        <v>10</v>
-      </c>
-      <c r="M12" s="2">
-        <v>0.94117647058823528</v>
-      </c>
-      <c r="N12" s="2">
-        <v>1.015154216914836</v>
-      </c>
-      <c r="O12" s="2">
-        <v>1.0666666666666671</v>
-      </c>
+      <c r="M12" s="2"/>
+      <c r="N12" s="2"/>
+      <c r="O12" s="2"/>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="B13" t="s">
-        <v>41</v>
+        <v>91</v>
       </c>
       <c r="C13" t="s">
         <v>38</v>
@@ -1608,16 +1456,16 @@
         <v>25</v>
       </c>
       <c r="E13">
-        <v>8</v>
+        <v>6.5</v>
       </c>
       <c r="F13">
+        <v>7.5</v>
+      </c>
+      <c r="G13">
+        <v>8.5</v>
+      </c>
+      <c r="H13">
         <v>9</v>
-      </c>
-      <c r="G13">
-        <v>10</v>
-      </c>
-      <c r="H13">
-        <v>10.5</v>
       </c>
       <c r="I13">
         <v>6.5</v>
@@ -1629,183 +1477,84 @@
         <v>8</v>
       </c>
       <c r="L13">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="M13" s="2">
-        <v>1.055555555555556</v>
+        <v>0.9375</v>
       </c>
       <c r="N13" s="2">
-        <v>1.25742253968254</v>
+        <v>1.030407619047619</v>
       </c>
       <c r="O13" s="2">
-        <v>1.461538461538461</v>
+        <v>1.125</v>
       </c>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>42</v>
+        <v>92</v>
       </c>
       <c r="B14" t="s">
-        <v>43</v>
+        <v>91</v>
       </c>
       <c r="C14" t="s">
-        <v>28</v>
-      </c>
-      <c r="D14">
-        <v>25</v>
-      </c>
-      <c r="E14">
-        <v>9</v>
-      </c>
-      <c r="F14">
-        <v>9</v>
-      </c>
-      <c r="G14">
-        <v>11.5</v>
-      </c>
-      <c r="H14">
-        <v>12</v>
-      </c>
-      <c r="I14">
-        <v>8</v>
-      </c>
-      <c r="J14">
-        <v>8.5</v>
-      </c>
-      <c r="K14">
-        <v>11</v>
-      </c>
-      <c r="L14">
-        <v>12</v>
-      </c>
-      <c r="M14" s="2">
-        <v>0.94736842105263153</v>
-      </c>
-      <c r="N14" s="2">
-        <v>1.0327935505430239</v>
-      </c>
-      <c r="O14" s="2">
-        <v>1.2777777777777779</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="M14" s="2"/>
+      <c r="N14" s="2"/>
+      <c r="O14" s="2"/>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>44</v>
+        <v>94</v>
       </c>
       <c r="B15" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="C15" t="s">
-        <v>28</v>
-      </c>
-      <c r="D15">
-        <v>25</v>
-      </c>
-      <c r="E15">
-        <v>10</v>
-      </c>
-      <c r="F15">
-        <v>10</v>
-      </c>
-      <c r="G15">
-        <v>12</v>
-      </c>
-      <c r="H15">
-        <v>14</v>
-      </c>
-      <c r="I15">
-        <v>10.5</v>
-      </c>
-      <c r="J15">
-        <v>11</v>
-      </c>
-      <c r="K15">
-        <v>12</v>
-      </c>
-      <c r="L15">
-        <v>14</v>
-      </c>
-      <c r="M15" s="2">
-        <v>0.86956521739130432</v>
-      </c>
-      <c r="N15" s="2">
-        <v>0.95759375117635992</v>
-      </c>
-      <c r="O15" s="2">
-        <v>1.0909090909090911</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="M15" s="2"/>
+      <c r="N15" s="2"/>
+      <c r="O15" s="2"/>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>46</v>
+        <v>111</v>
       </c>
       <c r="B16" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="C16" t="s">
-        <v>19</v>
-      </c>
-      <c r="D16">
-        <v>25</v>
-      </c>
-      <c r="E16">
-        <v>8.5</v>
-      </c>
-      <c r="F16">
-        <v>9</v>
-      </c>
-      <c r="G16">
-        <v>10.5</v>
-      </c>
-      <c r="H16">
-        <v>11.5</v>
-      </c>
-      <c r="I16">
-        <v>8</v>
-      </c>
-      <c r="J16">
-        <v>8.5</v>
-      </c>
-      <c r="K16">
-        <v>10.5</v>
-      </c>
-      <c r="L16">
-        <v>11.5</v>
-      </c>
-      <c r="M16" s="2">
-        <v>0.89473684210526316</v>
-      </c>
-      <c r="N16" s="2">
-        <v>1.0275120223639</v>
-      </c>
-      <c r="O16" s="2">
-        <v>1.125</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="M16" s="2"/>
+      <c r="N16" s="2"/>
+      <c r="O16" s="2"/>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>48</v>
+        <v>122</v>
       </c>
       <c r="B17" t="s">
-        <v>41</v>
+        <v>91</v>
       </c>
       <c r="C17" t="s">
         <v>38</v>
       </c>
       <c r="D17">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="E17">
+        <v>8</v>
+      </c>
+      <c r="F17">
+        <v>8.5</v>
+      </c>
+      <c r="G17">
         <v>10</v>
       </c>
-      <c r="F17">
+      <c r="H17">
         <v>10</v>
-      </c>
-      <c r="G17">
-        <v>12</v>
-      </c>
-      <c r="H17">
-        <v>13</v>
       </c>
       <c r="I17">
         <v>8</v>
@@ -1814,171 +1563,72 @@
         <v>8.5</v>
       </c>
       <c r="K17">
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="L17">
         <v>10</v>
       </c>
       <c r="M17" s="2">
-        <v>1.1000000000000001</v>
+        <v>1</v>
       </c>
       <c r="N17" s="2">
-        <v>1.283467877536979</v>
+        <v>1.039860901625608</v>
       </c>
       <c r="O17" s="2">
-        <v>1.4375</v>
+        <v>1.117647058823529</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>49</v>
+        <v>134</v>
       </c>
       <c r="B18" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="C18" t="s">
         <v>38</v>
       </c>
-      <c r="D18">
-        <v>25</v>
-      </c>
-      <c r="E18">
-        <v>10</v>
-      </c>
-      <c r="F18">
-        <v>10.5</v>
-      </c>
-      <c r="G18">
-        <v>12</v>
-      </c>
-      <c r="H18">
-        <v>12</v>
-      </c>
-      <c r="I18">
-        <v>7.5</v>
-      </c>
-      <c r="J18">
-        <v>7.5</v>
-      </c>
-      <c r="K18">
-        <v>8.5</v>
-      </c>
-      <c r="L18">
-        <v>9</v>
-      </c>
-      <c r="M18" s="2">
-        <v>1.2352941176470591</v>
-      </c>
-      <c r="N18" s="2">
-        <v>1.365101568627451</v>
-      </c>
-      <c r="O18" s="2">
-        <v>1.533333333333333</v>
-      </c>
+      <c r="M18" s="2"/>
+      <c r="N18" s="2"/>
+      <c r="O18" s="2"/>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>50</v>
+        <v>180</v>
       </c>
       <c r="B19" t="s">
-        <v>51</v>
+        <v>85</v>
       </c>
       <c r="C19" t="s">
-        <v>28</v>
-      </c>
-      <c r="D19">
-        <v>25</v>
-      </c>
-      <c r="E19">
-        <v>10.5</v>
-      </c>
-      <c r="F19">
-        <v>11.5</v>
-      </c>
-      <c r="G19">
-        <v>13</v>
-      </c>
-      <c r="H19">
-        <v>14</v>
-      </c>
-      <c r="I19">
-        <v>10.5</v>
-      </c>
-      <c r="J19">
-        <v>11</v>
-      </c>
-      <c r="K19">
-        <v>13</v>
-      </c>
-      <c r="L19">
-        <v>14.5</v>
-      </c>
-      <c r="M19" s="2">
-        <v>0.92307692307692313</v>
-      </c>
-      <c r="N19" s="2">
-        <v>1.0190771859784391</v>
-      </c>
-      <c r="O19" s="2">
-        <v>1.142857142857143</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="M19" s="2"/>
+      <c r="N19" s="2"/>
+      <c r="O19" s="2"/>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>52</v>
+        <v>181</v>
       </c>
       <c r="B20" t="s">
-        <v>53</v>
+        <v>85</v>
       </c>
       <c r="C20" t="s">
-        <v>19</v>
-      </c>
-      <c r="D20">
-        <v>25</v>
-      </c>
-      <c r="E20">
-        <v>7.5</v>
-      </c>
-      <c r="F20">
-        <v>8</v>
-      </c>
-      <c r="G20">
-        <v>9.5</v>
-      </c>
-      <c r="H20">
-        <v>10.5</v>
-      </c>
-      <c r="I20">
-        <v>7.5</v>
-      </c>
-      <c r="J20">
-        <v>7.5</v>
-      </c>
-      <c r="K20">
-        <v>9.5</v>
-      </c>
-      <c r="L20">
-        <v>10</v>
-      </c>
-      <c r="M20" s="2">
-        <v>0.94444444444444442</v>
-      </c>
-      <c r="N20" s="2">
-        <v>1.046760522875817</v>
-      </c>
-      <c r="O20" s="2">
-        <v>1.1875</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="M20" s="2"/>
+      <c r="N20" s="2"/>
+      <c r="O20" s="2"/>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>54</v>
+        <v>182</v>
       </c>
       <c r="B21" t="s">
-        <v>18</v>
+        <v>85</v>
       </c>
       <c r="C21" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="M21" s="2"/>
       <c r="N21" s="2"/>
@@ -1986,60 +1636,27 @@
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>55</v>
+        <v>183</v>
       </c>
       <c r="B22" t="s">
-        <v>56</v>
+        <v>91</v>
       </c>
       <c r="C22" t="s">
-        <v>57</v>
-      </c>
-      <c r="D22">
-        <v>25</v>
-      </c>
-      <c r="E22">
-        <v>7.5</v>
-      </c>
-      <c r="F22">
-        <v>8</v>
-      </c>
-      <c r="G22">
-        <v>9.5</v>
-      </c>
-      <c r="H22">
-        <v>11</v>
-      </c>
-      <c r="I22">
-        <v>7</v>
-      </c>
-      <c r="J22">
-        <v>7.5</v>
-      </c>
-      <c r="K22">
-        <v>8.5</v>
-      </c>
-      <c r="L22">
-        <v>10</v>
-      </c>
-      <c r="M22" s="2">
-        <v>0.85</v>
-      </c>
-      <c r="N22" s="2">
-        <v>1.096120802987862</v>
-      </c>
-      <c r="O22" s="2">
-        <v>1.2666666666666671</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="M22" s="2"/>
+      <c r="N22" s="2"/>
+      <c r="O22" s="2"/>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>58</v>
+        <v>192</v>
       </c>
       <c r="B23" t="s">
-        <v>59</v>
+        <v>91</v>
       </c>
       <c r="C23" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="M23" s="2"/>
       <c r="N23" s="2"/>
@@ -2047,263 +1664,131 @@
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="B24" t="s">
-        <v>53</v>
+        <v>71</v>
       </c>
       <c r="C24" t="s">
-        <v>19</v>
+        <v>72</v>
       </c>
       <c r="D24">
         <v>25</v>
       </c>
       <c r="E24">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F24">
-        <v>10.5</v>
+        <v>9.5</v>
       </c>
       <c r="G24">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="H24">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I24">
-        <v>8</v>
+        <v>5.5</v>
       </c>
       <c r="J24">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="K24">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="L24">
-        <v>11.5</v>
+        <v>7</v>
       </c>
       <c r="M24" s="2">
-        <v>1</v>
+        <v>1.428571428571429</v>
       </c>
       <c r="N24" s="2">
-        <v>1.169432968812794</v>
+        <v>1.6113939393939389</v>
       </c>
       <c r="O24" s="2">
-        <v>1.444444444444444</v>
+        <v>1.916666666666667</v>
       </c>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>61</v>
+        <v>149</v>
       </c>
       <c r="B25" t="s">
-        <v>53</v>
+        <v>71</v>
       </c>
       <c r="C25" t="s">
-        <v>19</v>
-      </c>
-      <c r="D25">
-        <v>25</v>
-      </c>
-      <c r="E25">
-        <v>8.5</v>
-      </c>
-      <c r="F25">
-        <v>9.5</v>
-      </c>
-      <c r="G25">
-        <v>11</v>
-      </c>
-      <c r="H25">
-        <v>11</v>
-      </c>
-      <c r="I25">
-        <v>8.5</v>
-      </c>
-      <c r="J25">
-        <v>8.5</v>
-      </c>
-      <c r="K25">
-        <v>10.5</v>
-      </c>
-      <c r="L25">
-        <v>11</v>
-      </c>
-      <c r="M25" s="2">
-        <v>0.90476190476190477</v>
-      </c>
-      <c r="N25" s="2">
-        <v>1.0557871275473749</v>
-      </c>
-      <c r="O25" s="2">
-        <v>1.2222222222222221</v>
-      </c>
+        <v>72</v>
+      </c>
+      <c r="M25" s="2"/>
+      <c r="N25" s="2"/>
+      <c r="O25" s="2"/>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>62</v>
+        <v>195</v>
       </c>
       <c r="B26" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="C26" t="s">
-        <v>57</v>
-      </c>
-      <c r="D26">
-        <v>25</v>
-      </c>
-      <c r="E26">
-        <v>7</v>
-      </c>
-      <c r="F26">
-        <v>7</v>
-      </c>
-      <c r="G26">
-        <v>9</v>
-      </c>
-      <c r="H26">
-        <v>10</v>
-      </c>
-      <c r="I26">
-        <v>6</v>
-      </c>
-      <c r="J26">
-        <v>6.5</v>
-      </c>
-      <c r="K26">
-        <v>8</v>
-      </c>
-      <c r="L26">
-        <v>9</v>
-      </c>
-      <c r="M26" s="2">
-        <v>0.93333333333333335</v>
-      </c>
-      <c r="N26" s="2">
-        <v>1.1055326984126981</v>
-      </c>
-      <c r="O26" s="2">
-        <v>1.333333333333333</v>
-      </c>
+        <v>72</v>
+      </c>
+      <c r="M26" s="2"/>
+      <c r="N26" s="2"/>
+      <c r="O26" s="2"/>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>63</v>
+        <v>107</v>
       </c>
       <c r="B27" t="s">
-        <v>56</v>
+        <v>108</v>
       </c>
       <c r="C27" t="s">
-        <v>57</v>
-      </c>
-      <c r="D27">
-        <v>25</v>
-      </c>
-      <c r="E27">
-        <v>6.5</v>
-      </c>
-      <c r="F27">
-        <v>7</v>
-      </c>
-      <c r="G27">
-        <v>10.5</v>
-      </c>
-      <c r="H27">
-        <v>12</v>
-      </c>
-      <c r="I27">
-        <v>6</v>
-      </c>
-      <c r="J27">
-        <v>6</v>
-      </c>
-      <c r="K27">
-        <v>8.5</v>
-      </c>
-      <c r="L27">
-        <v>9.5</v>
-      </c>
-      <c r="M27" s="2">
-        <v>1</v>
-      </c>
-      <c r="N27" s="2">
-        <v>1.204674427244582</v>
-      </c>
-      <c r="O27" s="2">
-        <v>1.6</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="M27" s="2"/>
+      <c r="N27" s="2"/>
+      <c r="O27" s="2"/>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>64</v>
+        <v>191</v>
       </c>
       <c r="B28" t="s">
-        <v>59</v>
+        <v>108</v>
       </c>
       <c r="C28" t="s">
-        <v>57</v>
-      </c>
-      <c r="D28">
-        <v>25</v>
-      </c>
-      <c r="E28">
-        <v>8</v>
-      </c>
-      <c r="F28">
-        <v>8.5</v>
-      </c>
-      <c r="G28">
-        <v>10</v>
-      </c>
-      <c r="H28">
-        <v>10.5</v>
-      </c>
-      <c r="I28">
-        <v>8</v>
-      </c>
-      <c r="J28">
-        <v>8.5</v>
-      </c>
-      <c r="K28">
-        <v>10</v>
-      </c>
-      <c r="L28">
-        <v>10.5</v>
-      </c>
-      <c r="M28" s="2">
-        <v>0.94736842105263153</v>
-      </c>
-      <c r="N28" s="2">
-        <v>1.0114234920634919</v>
-      </c>
-      <c r="O28" s="2">
-        <v>1.055555555555556</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="M28" s="2"/>
+      <c r="N28" s="2"/>
+      <c r="O28" s="2"/>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>65</v>
+        <v>17</v>
       </c>
       <c r="B29" t="s">
-        <v>66</v>
+        <v>18</v>
       </c>
       <c r="C29" t="s">
-        <v>57</v>
+        <v>19</v>
       </c>
       <c r="D29">
         <v>25</v>
       </c>
       <c r="E29">
-        <v>8.5</v>
+        <v>7.5</v>
       </c>
       <c r="F29">
         <v>8.5</v>
       </c>
       <c r="G29">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="H29">
-        <v>11</v>
+        <v>14.5</v>
       </c>
       <c r="I29">
         <v>7</v>
@@ -2312,27 +1797,27 @@
         <v>8</v>
       </c>
       <c r="K29">
-        <v>9.5</v>
+        <v>11.5</v>
       </c>
       <c r="L29">
-        <v>9.5</v>
+        <v>12</v>
       </c>
       <c r="M29" s="2">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="N29" s="2">
-        <v>1.0802804776647501</v>
+        <v>1.0950696320018529</v>
       </c>
       <c r="O29" s="2">
-        <v>1.214285714285714</v>
+        <v>1.29</v>
       </c>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>67</v>
+        <v>20</v>
       </c>
       <c r="B30" t="s">
-        <v>47</v>
+        <v>21</v>
       </c>
       <c r="C30" t="s">
         <v>19</v>
@@ -2341,10 +1826,10 @@
         <v>25</v>
       </c>
       <c r="E30">
-        <v>9.5</v>
+        <v>8</v>
       </c>
       <c r="F30">
-        <v>9.5</v>
+        <v>9</v>
       </c>
       <c r="G30">
         <v>11.5</v>
@@ -2353,280 +1838,379 @@
         <v>12</v>
       </c>
       <c r="I30">
-        <v>8.5</v>
+        <v>7</v>
       </c>
       <c r="J30">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K30">
-        <v>10.5</v>
+        <v>9.5</v>
       </c>
       <c r="L30">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="M30" s="2">
-        <v>1</v>
+        <v>1.0105263157894739</v>
       </c>
       <c r="N30" s="2">
-        <v>1.0795904742247779</v>
+        <v>1.1945087611067799</v>
       </c>
       <c r="O30" s="2">
-        <v>1.166666666666667</v>
+        <v>1.406976744186047</v>
       </c>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>68</v>
+        <v>25</v>
       </c>
       <c r="B31" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="C31" t="s">
-        <v>38</v>
-      </c>
-      <c r="M31" s="2"/>
-      <c r="N31" s="2"/>
-      <c r="O31" s="2"/>
+        <v>19</v>
+      </c>
+      <c r="D31">
+        <v>25</v>
+      </c>
+      <c r="E31">
+        <v>7.5</v>
+      </c>
+      <c r="F31">
+        <v>8.5</v>
+      </c>
+      <c r="G31">
+        <v>11</v>
+      </c>
+      <c r="H31">
+        <v>13</v>
+      </c>
+      <c r="I31">
+        <v>6</v>
+      </c>
+      <c r="J31">
+        <v>7</v>
+      </c>
+      <c r="K31">
+        <v>9.5</v>
+      </c>
+      <c r="L31">
+        <v>11</v>
+      </c>
+      <c r="M31" s="2">
+        <v>1.0476190476190479</v>
+      </c>
+      <c r="N31" s="2">
+        <v>1.211022792632205</v>
+      </c>
+      <c r="O31" s="2">
+        <v>1.4</v>
+      </c>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>69</v>
+        <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="C32" t="s">
-        <v>38</v>
-      </c>
-      <c r="M32" s="2"/>
-      <c r="N32" s="2"/>
-      <c r="O32" s="2"/>
+        <v>19</v>
+      </c>
+      <c r="D32">
+        <v>25</v>
+      </c>
+      <c r="E32">
+        <v>9</v>
+      </c>
+      <c r="F32">
+        <v>9</v>
+      </c>
+      <c r="G32">
+        <v>10.5</v>
+      </c>
+      <c r="H32">
+        <v>11.5</v>
+      </c>
+      <c r="I32">
+        <v>7.5</v>
+      </c>
+      <c r="J32">
+        <v>8.5</v>
+      </c>
+      <c r="K32">
+        <v>9.5</v>
+      </c>
+      <c r="L32">
+        <v>10</v>
+      </c>
+      <c r="M32" s="2">
+        <v>1</v>
+      </c>
+      <c r="N32" s="2">
+        <v>1.120581740626075</v>
+      </c>
+      <c r="O32" s="2">
+        <v>1.2666666666666671</v>
+      </c>
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>70</v>
+        <v>46</v>
       </c>
       <c r="B33" t="s">
-        <v>71</v>
+        <v>47</v>
       </c>
       <c r="C33" t="s">
-        <v>72</v>
+        <v>19</v>
       </c>
       <c r="D33">
         <v>25</v>
       </c>
       <c r="E33">
+        <v>8.5</v>
+      </c>
+      <c r="F33">
         <v>9</v>
       </c>
-      <c r="F33">
-        <v>9.5</v>
-      </c>
       <c r="G33">
+        <v>10.5</v>
+      </c>
+      <c r="H33">
         <v>11.5</v>
       </c>
-      <c r="H33">
-        <v>12</v>
-      </c>
       <c r="I33">
-        <v>5.5</v>
+        <v>8</v>
       </c>
       <c r="J33">
-        <v>6</v>
+        <v>8.5</v>
       </c>
       <c r="K33">
-        <v>7</v>
+        <v>10.5</v>
       </c>
       <c r="L33">
-        <v>7</v>
+        <v>11.5</v>
       </c>
       <c r="M33" s="2">
-        <v>1.428571428571429</v>
+        <v>0.89473684210526316</v>
       </c>
       <c r="N33" s="2">
-        <v>1.6113939393939389</v>
+        <v>1.0275120223639</v>
       </c>
       <c r="O33" s="2">
-        <v>1.916666666666667</v>
+        <v>1.125</v>
       </c>
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>73</v>
+        <v>52</v>
       </c>
       <c r="B34" t="s">
-        <v>66</v>
+        <v>53</v>
       </c>
       <c r="C34" t="s">
-        <v>57</v>
+        <v>19</v>
       </c>
       <c r="D34">
         <v>25</v>
       </c>
       <c r="E34">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="F34">
+        <v>8</v>
+      </c>
+      <c r="G34">
+        <v>9.5</v>
+      </c>
+      <c r="H34">
+        <v>10.5</v>
+      </c>
+      <c r="I34">
         <v>7.5</v>
-      </c>
-      <c r="G34">
-        <v>9</v>
-      </c>
-      <c r="H34">
-        <v>9.5</v>
-      </c>
-      <c r="I34">
-        <v>6.5</v>
       </c>
       <c r="J34">
         <v>7.5</v>
       </c>
       <c r="K34">
-        <v>8.5</v>
+        <v>9.5</v>
       </c>
       <c r="L34">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M34" s="2">
-        <v>0.94117647058823528</v>
+        <v>0.94444444444444442</v>
       </c>
       <c r="N34" s="2">
-        <v>1.050012661064426</v>
+        <v>1.046760522875817</v>
       </c>
       <c r="O34" s="2">
-        <v>1.142857142857143</v>
+        <v>1.1875</v>
       </c>
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>74</v>
+        <v>54</v>
       </c>
       <c r="B35" t="s">
-        <v>66</v>
+        <v>18</v>
       </c>
       <c r="C35" t="s">
-        <v>57</v>
-      </c>
-      <c r="D35">
-        <v>23</v>
-      </c>
-      <c r="E35">
-        <v>9</v>
-      </c>
-      <c r="F35">
-        <v>9</v>
-      </c>
-      <c r="G35">
-        <v>11</v>
-      </c>
-      <c r="H35">
-        <v>12</v>
-      </c>
-      <c r="I35">
-        <v>8.5</v>
-      </c>
-      <c r="J35">
-        <v>9</v>
-      </c>
-      <c r="K35">
-        <v>11</v>
-      </c>
-      <c r="L35">
-        <v>11</v>
-      </c>
-      <c r="M35" s="2">
-        <v>0.94736842105263153</v>
-      </c>
-      <c r="N35" s="2">
-        <v>1.031837163522487</v>
-      </c>
-      <c r="O35" s="2">
-        <v>1.2222222222222221</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="M35" s="2"/>
+      <c r="N35" s="2"/>
+      <c r="O35" s="2"/>
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="B36" t="s">
-        <v>76</v>
+        <v>53</v>
       </c>
       <c r="C36" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="D36">
         <v>25</v>
       </c>
       <c r="E36">
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="F36">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="G36">
+        <v>12.5</v>
+      </c>
+      <c r="H36">
         <v>13</v>
       </c>
-      <c r="H36">
-        <v>13.5</v>
-      </c>
       <c r="I36">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J36">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K36">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="L36">
-        <v>14</v>
+        <v>11.5</v>
       </c>
       <c r="M36" s="2">
-        <v>0.875</v>
+        <v>1</v>
       </c>
       <c r="N36" s="2">
-        <v>0.99257204592508941</v>
+        <v>1.169432968812794</v>
       </c>
       <c r="O36" s="2">
-        <v>1.1499999999999999</v>
+        <v>1.444444444444444</v>
       </c>
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>77</v>
+        <v>61</v>
       </c>
       <c r="B37" t="s">
-        <v>66</v>
+        <v>53</v>
       </c>
       <c r="C37" t="s">
-        <v>57</v>
-      </c>
-      <c r="M37" s="2"/>
-      <c r="N37" s="2"/>
-      <c r="O37" s="2"/>
+        <v>19</v>
+      </c>
+      <c r="D37">
+        <v>25</v>
+      </c>
+      <c r="E37">
+        <v>8.5</v>
+      </c>
+      <c r="F37">
+        <v>9.5</v>
+      </c>
+      <c r="G37">
+        <v>11</v>
+      </c>
+      <c r="H37">
+        <v>11</v>
+      </c>
+      <c r="I37">
+        <v>8.5</v>
+      </c>
+      <c r="J37">
+        <v>8.5</v>
+      </c>
+      <c r="K37">
+        <v>10.5</v>
+      </c>
+      <c r="L37">
+        <v>11</v>
+      </c>
+      <c r="M37" s="2">
+        <v>0.90476190476190477</v>
+      </c>
+      <c r="N37" s="2">
+        <v>1.0557871275473749</v>
+      </c>
+      <c r="O37" s="2">
+        <v>1.2222222222222221</v>
+      </c>
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="B38" t="s">
-        <v>66</v>
+        <v>47</v>
       </c>
       <c r="C38" t="s">
-        <v>57</v>
-      </c>
-      <c r="M38" s="2"/>
-      <c r="N38" s="2"/>
-      <c r="O38" s="2"/>
+        <v>19</v>
+      </c>
+      <c r="D38">
+        <v>25</v>
+      </c>
+      <c r="E38">
+        <v>9.5</v>
+      </c>
+      <c r="F38">
+        <v>9.5</v>
+      </c>
+      <c r="G38">
+        <v>11.5</v>
+      </c>
+      <c r="H38">
+        <v>12</v>
+      </c>
+      <c r="I38">
+        <v>8.5</v>
+      </c>
+      <c r="J38">
+        <v>9</v>
+      </c>
+      <c r="K38">
+        <v>10.5</v>
+      </c>
+      <c r="L38">
+        <v>11</v>
+      </c>
+      <c r="M38" s="2">
+        <v>1</v>
+      </c>
+      <c r="N38" s="2">
+        <v>1.0795904742247779</v>
+      </c>
+      <c r="O38" s="2">
+        <v>1.166666666666667</v>
+      </c>
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>79</v>
+        <v>110</v>
       </c>
       <c r="B39" t="s">
-        <v>66</v>
+        <v>18</v>
       </c>
       <c r="C39" t="s">
-        <v>57</v>
+        <v>19</v>
       </c>
       <c r="M39" s="2"/>
       <c r="N39" s="2"/>
@@ -2634,13 +2218,13 @@
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>80</v>
+        <v>140</v>
       </c>
       <c r="B40" t="s">
-        <v>66</v>
+        <v>47</v>
       </c>
       <c r="C40" t="s">
-        <v>57</v>
+        <v>19</v>
       </c>
       <c r="M40" s="2"/>
       <c r="N40" s="2"/>
@@ -2648,13 +2232,13 @@
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>81</v>
+        <v>143</v>
       </c>
       <c r="B41" t="s">
-        <v>76</v>
+        <v>47</v>
       </c>
       <c r="C41" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="M41" s="2"/>
       <c r="N41" s="2"/>
@@ -2662,13 +2246,13 @@
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>82</v>
+        <v>144</v>
       </c>
       <c r="B42" t="s">
-        <v>83</v>
+        <v>47</v>
       </c>
       <c r="C42" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="M42" s="2"/>
       <c r="N42" s="2"/>
@@ -2676,60 +2260,27 @@
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>84</v>
+        <v>148</v>
       </c>
       <c r="B43" t="s">
-        <v>85</v>
+        <v>18</v>
       </c>
       <c r="C43" t="s">
-        <v>38</v>
-      </c>
-      <c r="D43">
-        <v>21</v>
-      </c>
-      <c r="E43">
-        <v>9.5</v>
-      </c>
-      <c r="F43">
-        <v>10</v>
-      </c>
-      <c r="G43">
-        <v>11.5</v>
-      </c>
-      <c r="H43">
-        <v>12</v>
-      </c>
-      <c r="I43">
-        <v>7.5</v>
-      </c>
-      <c r="J43">
-        <v>8</v>
-      </c>
-      <c r="K43">
-        <v>9.5</v>
-      </c>
-      <c r="L43">
-        <v>9.5</v>
-      </c>
-      <c r="M43" s="2">
-        <v>1.0526315789473679</v>
-      </c>
-      <c r="N43" s="2">
-        <v>1.2309080018587919</v>
-      </c>
-      <c r="O43" s="2">
-        <v>1.4</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="M43" s="2"/>
+      <c r="N43" s="2"/>
+      <c r="O43" s="2"/>
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>86</v>
+        <v>150</v>
       </c>
       <c r="B44" t="s">
-        <v>85</v>
+        <v>18</v>
       </c>
       <c r="C44" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="M44" s="2"/>
       <c r="N44" s="2"/>
@@ -2737,13 +2288,13 @@
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>87</v>
+        <v>152</v>
       </c>
       <c r="B45" t="s">
-        <v>85</v>
+        <v>18</v>
       </c>
       <c r="C45" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="M45" s="2"/>
       <c r="N45" s="2"/>
@@ -2751,13 +2302,13 @@
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>88</v>
+        <v>155</v>
       </c>
       <c r="B46" t="s">
-        <v>89</v>
+        <v>53</v>
       </c>
       <c r="C46" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="M46" s="2"/>
       <c r="N46" s="2"/>
@@ -2765,60 +2316,27 @@
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>90</v>
+        <v>160</v>
       </c>
       <c r="B47" t="s">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="C47" t="s">
-        <v>38</v>
-      </c>
-      <c r="D47">
-        <v>25</v>
-      </c>
-      <c r="E47">
-        <v>6.5</v>
-      </c>
-      <c r="F47">
-        <v>7.5</v>
-      </c>
-      <c r="G47">
-        <v>8.5</v>
-      </c>
-      <c r="H47">
-        <v>9</v>
-      </c>
-      <c r="I47">
-        <v>6.5</v>
-      </c>
-      <c r="J47">
-        <v>7</v>
-      </c>
-      <c r="K47">
-        <v>8</v>
-      </c>
-      <c r="L47">
-        <v>8.5</v>
-      </c>
-      <c r="M47" s="2">
-        <v>0.9375</v>
-      </c>
-      <c r="N47" s="2">
-        <v>1.030407619047619</v>
-      </c>
-      <c r="O47" s="2">
-        <v>1.125</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="M47" s="2"/>
+      <c r="N47" s="2"/>
+      <c r="O47" s="2"/>
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>92</v>
+        <v>168</v>
       </c>
       <c r="B48" t="s">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="C48" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="M48" s="2"/>
       <c r="N48" s="2"/>
@@ -2826,13 +2344,13 @@
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>93</v>
+        <v>169</v>
       </c>
       <c r="B49" t="s">
-        <v>56</v>
+        <v>21</v>
       </c>
       <c r="C49" t="s">
-        <v>57</v>
+        <v>19</v>
       </c>
       <c r="M49" s="2"/>
       <c r="N49" s="2"/>
@@ -2840,13 +2358,13 @@
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>94</v>
+        <v>173</v>
       </c>
       <c r="B50" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="C50" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="M50" s="2"/>
       <c r="N50" s="2"/>
@@ -2854,60 +2372,27 @@
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>95</v>
+        <v>174</v>
       </c>
       <c r="B51" t="s">
-        <v>96</v>
+        <v>53</v>
       </c>
       <c r="C51" t="s">
-        <v>57</v>
-      </c>
-      <c r="D51">
-        <v>25</v>
-      </c>
-      <c r="E51">
-        <v>8</v>
-      </c>
-      <c r="F51">
-        <v>8</v>
-      </c>
-      <c r="G51">
-        <v>10</v>
-      </c>
-      <c r="H51">
-        <v>10</v>
-      </c>
-      <c r="I51">
-        <v>6</v>
-      </c>
-      <c r="J51">
-        <v>6</v>
-      </c>
-      <c r="K51">
-        <v>7.5</v>
-      </c>
-      <c r="L51">
-        <v>8</v>
-      </c>
-      <c r="M51" s="2">
-        <v>1.0666666666666671</v>
-      </c>
-      <c r="N51" s="2">
-        <v>1.2846247619047619</v>
-      </c>
-      <c r="O51" s="2">
-        <v>1.461538461538461</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="M51" s="2"/>
+      <c r="N51" s="2"/>
+      <c r="O51" s="2"/>
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>97</v>
+        <v>175</v>
       </c>
       <c r="B52" t="s">
-        <v>96</v>
+        <v>53</v>
       </c>
       <c r="C52" t="s">
-        <v>57</v>
+        <v>19</v>
       </c>
       <c r="M52" s="2"/>
       <c r="N52" s="2"/>
@@ -2915,13 +2400,13 @@
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>98</v>
+        <v>176</v>
       </c>
       <c r="B53" t="s">
-        <v>96</v>
+        <v>53</v>
       </c>
       <c r="C53" t="s">
-        <v>57</v>
+        <v>19</v>
       </c>
       <c r="M53" s="2"/>
       <c r="N53" s="2"/>
@@ -2929,13 +2414,13 @@
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>99</v>
+        <v>177</v>
       </c>
       <c r="B54" t="s">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="C54" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="M54" s="2"/>
       <c r="N54" s="2"/>
@@ -2943,13 +2428,13 @@
     </row>
     <row r="55" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
-        <v>100</v>
+        <v>178</v>
       </c>
       <c r="B55" t="s">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="C55" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="M55" s="2"/>
       <c r="N55" s="2"/>
@@ -2957,169 +2442,433 @@
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
-        <v>101</v>
+        <v>22</v>
       </c>
       <c r="B56" t="s">
-        <v>102</v>
+        <v>23</v>
       </c>
       <c r="C56" t="s">
-        <v>57</v>
-      </c>
-      <c r="M56" s="2"/>
-      <c r="N56" s="2"/>
-      <c r="O56" s="2"/>
+        <v>24</v>
+      </c>
+      <c r="D56">
+        <v>25</v>
+      </c>
+      <c r="E56">
+        <v>6</v>
+      </c>
+      <c r="F56">
+        <v>8.5</v>
+      </c>
+      <c r="G56">
+        <v>11.5</v>
+      </c>
+      <c r="H56">
+        <v>11.5</v>
+      </c>
+      <c r="I56">
+        <v>6.5</v>
+      </c>
+      <c r="J56">
+        <v>7</v>
+      </c>
+      <c r="K56">
+        <v>8</v>
+      </c>
+      <c r="L56">
+        <v>8</v>
+      </c>
+      <c r="M56" s="2">
+        <v>0.83783783783783783</v>
+      </c>
+      <c r="N56" s="2">
+        <v>1.327240994376564</v>
+      </c>
+      <c r="O56" s="2">
+        <v>1.567567567567568</v>
+      </c>
     </row>
     <row r="57" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
-        <v>103</v>
+        <v>26</v>
       </c>
       <c r="B57" t="s">
-        <v>102</v>
+        <v>27</v>
       </c>
       <c r="C57" t="s">
-        <v>57</v>
-      </c>
-      <c r="M57" s="2"/>
-      <c r="N57" s="2"/>
-      <c r="O57" s="2"/>
+        <v>28</v>
+      </c>
+      <c r="D57">
+        <v>25</v>
+      </c>
+      <c r="E57">
+        <v>9</v>
+      </c>
+      <c r="F57">
+        <v>9.5</v>
+      </c>
+      <c r="G57">
+        <v>11.5</v>
+      </c>
+      <c r="H57">
+        <v>12</v>
+      </c>
+      <c r="I57">
+        <v>8.5</v>
+      </c>
+      <c r="J57">
+        <v>9</v>
+      </c>
+      <c r="K57">
+        <v>10.5</v>
+      </c>
+      <c r="L57">
+        <v>11</v>
+      </c>
+      <c r="M57" s="2">
+        <v>1</v>
+      </c>
+      <c r="N57" s="2">
+        <v>1.1103157201381351</v>
+      </c>
+      <c r="O57" s="2">
+        <v>1.2777777777777779</v>
+      </c>
     </row>
     <row r="58" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
-        <v>104</v>
+        <v>29</v>
       </c>
       <c r="B58" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="C58" t="s">
         <v>28</v>
       </c>
-      <c r="M58" s="2"/>
-      <c r="N58" s="2"/>
-      <c r="O58" s="2"/>
+      <c r="D58">
+        <v>25</v>
+      </c>
+      <c r="E58">
+        <v>10</v>
+      </c>
+      <c r="F58">
+        <v>10.5</v>
+      </c>
+      <c r="G58">
+        <v>12</v>
+      </c>
+      <c r="H58">
+        <v>12.5</v>
+      </c>
+      <c r="I58">
+        <v>10</v>
+      </c>
+      <c r="J58">
+        <v>10.5</v>
+      </c>
+      <c r="K58">
+        <v>12</v>
+      </c>
+      <c r="L58">
+        <v>12.5</v>
+      </c>
+      <c r="M58" s="2">
+        <v>0.95238095238095233</v>
+      </c>
+      <c r="N58" s="2">
+        <v>1.004768966685488</v>
+      </c>
+      <c r="O58" s="2">
+        <v>1.1499999999999999</v>
+      </c>
     </row>
     <row r="59" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
-        <v>105</v>
+        <v>32</v>
       </c>
       <c r="B59" t="s">
-        <v>106</v>
+        <v>33</v>
       </c>
       <c r="C59" t="s">
-        <v>57</v>
+        <v>28</v>
       </c>
       <c r="D59">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="E59">
-        <v>6.5</v>
+        <v>9.5</v>
       </c>
       <c r="F59">
-        <v>6.5</v>
+        <v>10</v>
       </c>
       <c r="G59">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="H59">
+        <v>12</v>
+      </c>
+      <c r="I59">
         <v>9.5</v>
       </c>
-      <c r="I59">
-        <v>5</v>
-      </c>
       <c r="J59">
-        <v>5.5</v>
+        <v>10</v>
       </c>
       <c r="K59">
-        <v>6.5</v>
+        <v>11.5</v>
       </c>
       <c r="L59">
-        <v>7</v>
+        <v>12.5</v>
       </c>
       <c r="M59" s="2">
-        <v>1</v>
+        <v>0.95238095238095233</v>
       </c>
       <c r="N59" s="2">
-        <v>1.242687445887446</v>
+        <v>1.0124446213779961</v>
       </c>
       <c r="O59" s="2">
-        <v>1.6</v>
+        <v>1.0909090909090911</v>
       </c>
     </row>
     <row r="60" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
-        <v>107</v>
+        <v>34</v>
       </c>
       <c r="B60" t="s">
-        <v>108</v>
+        <v>35</v>
       </c>
       <c r="C60" t="s">
-        <v>109</v>
-      </c>
-      <c r="M60" s="2"/>
-      <c r="N60" s="2"/>
-      <c r="O60" s="2"/>
+        <v>28</v>
+      </c>
+      <c r="D60">
+        <v>25</v>
+      </c>
+      <c r="E60">
+        <v>7.5</v>
+      </c>
+      <c r="F60">
+        <v>10</v>
+      </c>
+      <c r="G60">
+        <v>11.5</v>
+      </c>
+      <c r="H60">
+        <v>12.5</v>
+      </c>
+      <c r="I60">
+        <v>8</v>
+      </c>
+      <c r="J60">
+        <v>9.5</v>
+      </c>
+      <c r="K60">
+        <v>11.5</v>
+      </c>
+      <c r="L60">
+        <v>12.5</v>
+      </c>
+      <c r="M60" s="2">
+        <v>0.9375</v>
+      </c>
+      <c r="N60" s="2">
+        <v>1.0023546248229269</v>
+      </c>
+      <c r="O60" s="2">
+        <v>1.0526315789473679</v>
+      </c>
     </row>
     <row r="61" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
-        <v>110</v>
+        <v>42</v>
       </c>
       <c r="B61" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="C61" t="s">
-        <v>19</v>
-      </c>
-      <c r="M61" s="2"/>
-      <c r="N61" s="2"/>
-      <c r="O61" s="2"/>
+        <v>28</v>
+      </c>
+      <c r="D61">
+        <v>25</v>
+      </c>
+      <c r="E61">
+        <v>9</v>
+      </c>
+      <c r="F61">
+        <v>9</v>
+      </c>
+      <c r="G61">
+        <v>11.5</v>
+      </c>
+      <c r="H61">
+        <v>12</v>
+      </c>
+      <c r="I61">
+        <v>8</v>
+      </c>
+      <c r="J61">
+        <v>8.5</v>
+      </c>
+      <c r="K61">
+        <v>11</v>
+      </c>
+      <c r="L61">
+        <v>12</v>
+      </c>
+      <c r="M61" s="2">
+        <v>0.94736842105263153</v>
+      </c>
+      <c r="N61" s="2">
+        <v>1.0327935505430239</v>
+      </c>
+      <c r="O61" s="2">
+        <v>1.2777777777777779</v>
+      </c>
     </row>
     <row r="62" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
-        <v>111</v>
+        <v>44</v>
       </c>
       <c r="B62" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="C62" t="s">
-        <v>38</v>
-      </c>
-      <c r="M62" s="2"/>
-      <c r="N62" s="2"/>
-      <c r="O62" s="2"/>
+        <v>28</v>
+      </c>
+      <c r="D62">
+        <v>25</v>
+      </c>
+      <c r="E62">
+        <v>10</v>
+      </c>
+      <c r="F62">
+        <v>10</v>
+      </c>
+      <c r="G62">
+        <v>12</v>
+      </c>
+      <c r="H62">
+        <v>14</v>
+      </c>
+      <c r="I62">
+        <v>10.5</v>
+      </c>
+      <c r="J62">
+        <v>11</v>
+      </c>
+      <c r="K62">
+        <v>12</v>
+      </c>
+      <c r="L62">
+        <v>14</v>
+      </c>
+      <c r="M62" s="2">
+        <v>0.86956521739130432</v>
+      </c>
+      <c r="N62" s="2">
+        <v>0.95759375117635992</v>
+      </c>
+      <c r="O62" s="2">
+        <v>1.0909090909090911</v>
+      </c>
     </row>
     <row r="63" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
-        <v>112</v>
+        <v>50</v>
       </c>
       <c r="B63" t="s">
-        <v>113</v>
+        <v>51</v>
       </c>
       <c r="C63" t="s">
         <v>28</v>
       </c>
-      <c r="M63" s="2"/>
-      <c r="N63" s="2"/>
-      <c r="O63" s="2"/>
+      <c r="D63">
+        <v>25</v>
+      </c>
+      <c r="E63">
+        <v>10.5</v>
+      </c>
+      <c r="F63">
+        <v>11.5</v>
+      </c>
+      <c r="G63">
+        <v>13</v>
+      </c>
+      <c r="H63">
+        <v>14</v>
+      </c>
+      <c r="I63">
+        <v>10.5</v>
+      </c>
+      <c r="J63">
+        <v>11</v>
+      </c>
+      <c r="K63">
+        <v>13</v>
+      </c>
+      <c r="L63">
+        <v>14.5</v>
+      </c>
+      <c r="M63" s="2">
+        <v>0.92307692307692313</v>
+      </c>
+      <c r="N63" s="2">
+        <v>1.0190771859784391</v>
+      </c>
+      <c r="O63" s="2">
+        <v>1.142857142857143</v>
+      </c>
     </row>
     <row r="64" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
-        <v>114</v>
+        <v>75</v>
       </c>
       <c r="B64" t="s">
-        <v>115</v>
+        <v>76</v>
       </c>
       <c r="C64" t="s">
         <v>28</v>
       </c>
-      <c r="M64" s="2"/>
-      <c r="N64" s="2"/>
-      <c r="O64" s="2"/>
+      <c r="D64">
+        <v>25</v>
+      </c>
+      <c r="E64">
+        <v>9.5</v>
+      </c>
+      <c r="F64">
+        <v>10</v>
+      </c>
+      <c r="G64">
+        <v>13</v>
+      </c>
+      <c r="H64">
+        <v>13.5</v>
+      </c>
+      <c r="I64">
+        <v>10</v>
+      </c>
+      <c r="J64">
+        <v>10</v>
+      </c>
+      <c r="K64">
+        <v>13</v>
+      </c>
+      <c r="L64">
+        <v>14</v>
+      </c>
+      <c r="M64" s="2">
+        <v>0.875</v>
+      </c>
+      <c r="N64" s="2">
+        <v>0.99257204592508941</v>
+      </c>
+      <c r="O64" s="2">
+        <v>1.1499999999999999</v>
+      </c>
     </row>
     <row r="65" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
-        <v>116</v>
+        <v>81</v>
       </c>
       <c r="B65" t="s">
-        <v>113</v>
+        <v>76</v>
       </c>
       <c r="C65" t="s">
         <v>28</v>
@@ -3130,13 +2879,13 @@
     </row>
     <row r="66" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
-        <v>117</v>
+        <v>88</v>
       </c>
       <c r="B66" t="s">
-        <v>118</v>
+        <v>89</v>
       </c>
       <c r="C66" t="s">
-        <v>57</v>
+        <v>28</v>
       </c>
       <c r="M66" s="2"/>
       <c r="N66" s="2"/>
@@ -3144,10 +2893,10 @@
     </row>
     <row r="67" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
-        <v>119</v>
+        <v>99</v>
       </c>
       <c r="B67" t="s">
-        <v>120</v>
+        <v>35</v>
       </c>
       <c r="C67" t="s">
         <v>28</v>
@@ -3158,13 +2907,13 @@
     </row>
     <row r="68" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
-        <v>121</v>
+        <v>100</v>
       </c>
       <c r="B68" t="s">
-        <v>118</v>
+        <v>35</v>
       </c>
       <c r="C68" t="s">
-        <v>57</v>
+        <v>28</v>
       </c>
       <c r="M68" s="2"/>
       <c r="N68" s="2"/>
@@ -3172,57 +2921,24 @@
     </row>
     <row r="69" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
-        <v>122</v>
+        <v>104</v>
       </c>
       <c r="B69" t="s">
-        <v>91</v>
+        <v>43</v>
       </c>
       <c r="C69" t="s">
-        <v>38</v>
-      </c>
-      <c r="D69">
-        <v>20</v>
-      </c>
-      <c r="E69">
-        <v>8</v>
-      </c>
-      <c r="F69">
-        <v>8.5</v>
-      </c>
-      <c r="G69">
-        <v>10</v>
-      </c>
-      <c r="H69">
-        <v>10</v>
-      </c>
-      <c r="I69">
-        <v>8</v>
-      </c>
-      <c r="J69">
-        <v>8.5</v>
-      </c>
-      <c r="K69">
-        <v>9.5</v>
-      </c>
-      <c r="L69">
-        <v>10</v>
-      </c>
-      <c r="M69" s="2">
-        <v>1</v>
-      </c>
-      <c r="N69" s="2">
-        <v>1.039860901625608</v>
-      </c>
-      <c r="O69" s="2">
-        <v>1.117647058823529</v>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="M69" s="2"/>
+      <c r="N69" s="2"/>
+      <c r="O69" s="2"/>
     </row>
     <row r="70" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="B70" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C70" t="s">
         <v>28</v>
@@ -3233,10 +2949,10 @@
     </row>
     <row r="71" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="B71" t="s">
-        <v>89</v>
+        <v>115</v>
       </c>
       <c r="C71" t="s">
         <v>28</v>
@@ -3247,13 +2963,13 @@
     </row>
     <row r="72" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="B72" t="s">
-        <v>96</v>
+        <v>113</v>
       </c>
       <c r="C72" t="s">
-        <v>57</v>
+        <v>28</v>
       </c>
       <c r="M72" s="2"/>
       <c r="N72" s="2"/>
@@ -3261,13 +2977,13 @@
     </row>
     <row r="73" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="B73" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C73" t="s">
-        <v>57</v>
+        <v>28</v>
       </c>
       <c r="M73" s="2"/>
       <c r="N73" s="2"/>
@@ -3275,13 +2991,13 @@
     </row>
     <row r="74" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="B74" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="C74" t="s">
-        <v>57</v>
+        <v>28</v>
       </c>
       <c r="M74" s="2"/>
       <c r="N74" s="2"/>
@@ -3289,10 +3005,10 @@
     </row>
     <row r="75" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="B75" t="s">
-        <v>113</v>
+        <v>89</v>
       </c>
       <c r="C75" t="s">
         <v>28</v>
@@ -3303,10 +3019,10 @@
     </row>
     <row r="76" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B76" t="s">
-        <v>35</v>
+        <v>113</v>
       </c>
       <c r="C76" t="s">
         <v>28</v>
@@ -3317,10 +3033,10 @@
     </row>
     <row r="77" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B77" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="C77" t="s">
         <v>28</v>
@@ -3331,13 +3047,13 @@
     </row>
     <row r="78" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B78" t="s">
-        <v>118</v>
+        <v>43</v>
       </c>
       <c r="C78" t="s">
-        <v>57</v>
+        <v>28</v>
       </c>
       <c r="M78" s="2"/>
       <c r="N78" s="2"/>
@@ -3345,13 +3061,13 @@
     </row>
     <row r="79" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="B79" t="s">
-        <v>118</v>
+        <v>136</v>
       </c>
       <c r="C79" t="s">
-        <v>57</v>
+        <v>28</v>
       </c>
       <c r="M79" s="2"/>
       <c r="N79" s="2"/>
@@ -3359,13 +3075,13 @@
     </row>
     <row r="80" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="B80" t="s">
-        <v>102</v>
+        <v>142</v>
       </c>
       <c r="C80" t="s">
-        <v>57</v>
+        <v>28</v>
       </c>
       <c r="M80" s="2"/>
       <c r="N80" s="2"/>
@@ -3373,13 +3089,13 @@
     </row>
     <row r="81" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
-        <v>134</v>
+        <v>153</v>
       </c>
       <c r="B81" t="s">
-        <v>37</v>
+        <v>154</v>
       </c>
       <c r="C81" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="M81" s="2"/>
       <c r="N81" s="2"/>
@@ -3387,10 +3103,10 @@
     </row>
     <row r="82" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
-        <v>135</v>
+        <v>156</v>
       </c>
       <c r="B82" t="s">
-        <v>136</v>
+        <v>89</v>
       </c>
       <c r="C82" t="s">
         <v>28</v>
@@ -3401,13 +3117,13 @@
     </row>
     <row r="83" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
-        <v>137</v>
+        <v>157</v>
       </c>
       <c r="B83" t="s">
-        <v>118</v>
+        <v>30</v>
       </c>
       <c r="C83" t="s">
-        <v>57</v>
+        <v>28</v>
       </c>
       <c r="M83" s="2"/>
       <c r="N83" s="2"/>
@@ -3415,13 +3131,13 @@
     </row>
     <row r="84" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
-        <v>138</v>
+        <v>158</v>
       </c>
       <c r="B84" t="s">
-        <v>96</v>
+        <v>30</v>
       </c>
       <c r="C84" t="s">
-        <v>57</v>
+        <v>28</v>
       </c>
       <c r="M84" s="2"/>
       <c r="N84" s="2"/>
@@ -3429,13 +3145,13 @@
     </row>
     <row r="85" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
-        <v>139</v>
+        <v>161</v>
       </c>
       <c r="B85" t="s">
-        <v>118</v>
+        <v>30</v>
       </c>
       <c r="C85" t="s">
-        <v>57</v>
+        <v>28</v>
       </c>
       <c r="M85" s="2"/>
       <c r="N85" s="2"/>
@@ -3443,13 +3159,13 @@
     </row>
     <row r="86" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
-        <v>140</v>
+        <v>170</v>
       </c>
       <c r="B86" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C86" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="M86" s="2"/>
       <c r="N86" s="2"/>
@@ -3457,10 +3173,10 @@
     </row>
     <row r="87" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
-        <v>141</v>
+        <v>171</v>
       </c>
       <c r="B87" t="s">
-        <v>142</v>
+        <v>43</v>
       </c>
       <c r="C87" t="s">
         <v>28</v>
@@ -3471,13 +3187,13 @@
     </row>
     <row r="88" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
-        <v>143</v>
+        <v>172</v>
       </c>
       <c r="B88" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C88" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="M88" s="2"/>
       <c r="N88" s="2"/>
@@ -3485,13 +3201,13 @@
     </row>
     <row r="89" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
-        <v>144</v>
+        <v>193</v>
       </c>
       <c r="B89" t="s">
-        <v>47</v>
+        <v>115</v>
       </c>
       <c r="C89" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="M89" s="2"/>
       <c r="N89" s="2"/>
@@ -3499,13 +3215,13 @@
     </row>
     <row r="90" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
-        <v>145</v>
+        <v>194</v>
       </c>
       <c r="B90" t="s">
-        <v>146</v>
+        <v>43</v>
       </c>
       <c r="C90" t="s">
-        <v>57</v>
+        <v>28</v>
       </c>
       <c r="M90" s="2"/>
       <c r="N90" s="2"/>
@@ -3513,13 +3229,13 @@
     </row>
     <row r="91" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
-        <v>147</v>
+        <v>196</v>
       </c>
       <c r="B91" t="s">
-        <v>118</v>
+        <v>89</v>
       </c>
       <c r="C91" t="s">
-        <v>57</v>
+        <v>28</v>
       </c>
       <c r="M91" s="2"/>
       <c r="N91" s="2"/>
@@ -3527,13 +3243,13 @@
     </row>
     <row r="92" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
-        <v>148</v>
+        <v>197</v>
       </c>
       <c r="B92" t="s">
-        <v>18</v>
+        <v>89</v>
       </c>
       <c r="C92" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="M92" s="2"/>
       <c r="N92" s="2"/>
@@ -3541,13 +3257,13 @@
     </row>
     <row r="93" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
-        <v>149</v>
+        <v>198</v>
       </c>
       <c r="B93" t="s">
-        <v>71</v>
+        <v>89</v>
       </c>
       <c r="C93" t="s">
-        <v>72</v>
+        <v>28</v>
       </c>
       <c r="M93" s="2"/>
       <c r="N93" s="2"/>
@@ -3555,13 +3271,13 @@
     </row>
     <row r="94" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
-        <v>150</v>
+        <v>199</v>
       </c>
       <c r="B94" t="s">
-        <v>18</v>
+        <v>89</v>
       </c>
       <c r="C94" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="M94" s="2"/>
       <c r="N94" s="2"/>
@@ -3569,13 +3285,13 @@
     </row>
     <row r="95" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
-        <v>151</v>
+        <v>200</v>
       </c>
       <c r="B95" t="s">
-        <v>71</v>
+        <v>89</v>
       </c>
       <c r="C95" t="s">
-        <v>57</v>
+        <v>28</v>
       </c>
       <c r="M95" s="2"/>
       <c r="N95" s="2"/>
@@ -3583,13 +3299,13 @@
     </row>
     <row r="96" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
-        <v>152</v>
+        <v>201</v>
       </c>
       <c r="B96" t="s">
-        <v>18</v>
+        <v>89</v>
       </c>
       <c r="C96" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="M96" s="2"/>
       <c r="N96" s="2"/>
@@ -3597,27 +3313,60 @@
     </row>
     <row r="97" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
-        <v>153</v>
+        <v>55</v>
       </c>
       <c r="B97" t="s">
-        <v>154</v>
+        <v>56</v>
       </c>
       <c r="C97" t="s">
-        <v>28</v>
-      </c>
-      <c r="M97" s="2"/>
-      <c r="N97" s="2"/>
-      <c r="O97" s="2"/>
+        <v>57</v>
+      </c>
+      <c r="D97">
+        <v>25</v>
+      </c>
+      <c r="E97">
+        <v>7.5</v>
+      </c>
+      <c r="F97">
+        <v>8</v>
+      </c>
+      <c r="G97">
+        <v>9.5</v>
+      </c>
+      <c r="H97">
+        <v>11</v>
+      </c>
+      <c r="I97">
+        <v>7</v>
+      </c>
+      <c r="J97">
+        <v>7.5</v>
+      </c>
+      <c r="K97">
+        <v>8.5</v>
+      </c>
+      <c r="L97">
+        <v>10</v>
+      </c>
+      <c r="M97" s="2">
+        <v>0.85</v>
+      </c>
+      <c r="N97" s="2">
+        <v>1.096120802987862</v>
+      </c>
+      <c r="O97" s="2">
+        <v>1.2666666666666671</v>
+      </c>
     </row>
     <row r="98" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
-        <v>155</v>
+        <v>58</v>
       </c>
       <c r="B98" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="C98" t="s">
-        <v>19</v>
+        <v>57</v>
       </c>
       <c r="M98" s="2"/>
       <c r="N98" s="2"/>
@@ -3625,94 +3374,292 @@
     </row>
     <row r="99" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
-        <v>156</v>
+        <v>62</v>
       </c>
       <c r="B99" t="s">
-        <v>89</v>
+        <v>56</v>
       </c>
       <c r="C99" t="s">
-        <v>28</v>
-      </c>
-      <c r="M99" s="2"/>
-      <c r="N99" s="2"/>
-      <c r="O99" s="2"/>
+        <v>57</v>
+      </c>
+      <c r="D99">
+        <v>25</v>
+      </c>
+      <c r="E99">
+        <v>7</v>
+      </c>
+      <c r="F99">
+        <v>7</v>
+      </c>
+      <c r="G99">
+        <v>9</v>
+      </c>
+      <c r="H99">
+        <v>10</v>
+      </c>
+      <c r="I99">
+        <v>6</v>
+      </c>
+      <c r="J99">
+        <v>6.5</v>
+      </c>
+      <c r="K99">
+        <v>8</v>
+      </c>
+      <c r="L99">
+        <v>9</v>
+      </c>
+      <c r="M99" s="2">
+        <v>0.93333333333333335</v>
+      </c>
+      <c r="N99" s="2">
+        <v>1.1055326984126981</v>
+      </c>
+      <c r="O99" s="2">
+        <v>1.333333333333333</v>
+      </c>
     </row>
     <row r="100" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
-        <v>157</v>
+        <v>63</v>
       </c>
       <c r="B100" t="s">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="C100" t="s">
-        <v>28</v>
-      </c>
-      <c r="M100" s="2"/>
-      <c r="N100" s="2"/>
-      <c r="O100" s="2"/>
+        <v>57</v>
+      </c>
+      <c r="D100">
+        <v>25</v>
+      </c>
+      <c r="E100">
+        <v>6.5</v>
+      </c>
+      <c r="F100">
+        <v>7</v>
+      </c>
+      <c r="G100">
+        <v>10.5</v>
+      </c>
+      <c r="H100">
+        <v>12</v>
+      </c>
+      <c r="I100">
+        <v>6</v>
+      </c>
+      <c r="J100">
+        <v>6</v>
+      </c>
+      <c r="K100">
+        <v>8.5</v>
+      </c>
+      <c r="L100">
+        <v>9.5</v>
+      </c>
+      <c r="M100" s="2">
+        <v>1</v>
+      </c>
+      <c r="N100" s="2">
+        <v>1.204674427244582</v>
+      </c>
+      <c r="O100" s="2">
+        <v>1.6</v>
+      </c>
     </row>
     <row r="101" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
-        <v>158</v>
+        <v>64</v>
       </c>
       <c r="B101" t="s">
-        <v>30</v>
+        <v>59</v>
       </c>
       <c r="C101" t="s">
-        <v>28</v>
-      </c>
-      <c r="M101" s="2"/>
-      <c r="N101" s="2"/>
-      <c r="O101" s="2"/>
+        <v>57</v>
+      </c>
+      <c r="D101">
+        <v>25</v>
+      </c>
+      <c r="E101">
+        <v>8</v>
+      </c>
+      <c r="F101">
+        <v>8.5</v>
+      </c>
+      <c r="G101">
+        <v>10</v>
+      </c>
+      <c r="H101">
+        <v>10.5</v>
+      </c>
+      <c r="I101">
+        <v>8</v>
+      </c>
+      <c r="J101">
+        <v>8.5</v>
+      </c>
+      <c r="K101">
+        <v>10</v>
+      </c>
+      <c r="L101">
+        <v>10.5</v>
+      </c>
+      <c r="M101" s="2">
+        <v>0.94736842105263153</v>
+      </c>
+      <c r="N101" s="2">
+        <v>1.0114234920634919</v>
+      </c>
+      <c r="O101" s="2">
+        <v>1.055555555555556</v>
+      </c>
     </row>
     <row r="102" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
-        <v>159</v>
+        <v>65</v>
       </c>
       <c r="B102" t="s">
-        <v>106</v>
+        <v>66</v>
       </c>
       <c r="C102" t="s">
         <v>57</v>
       </c>
-      <c r="M102" s="2"/>
-      <c r="N102" s="2"/>
-      <c r="O102" s="2"/>
+      <c r="D102">
+        <v>25</v>
+      </c>
+      <c r="E102">
+        <v>8.5</v>
+      </c>
+      <c r="F102">
+        <v>8.5</v>
+      </c>
+      <c r="G102">
+        <v>10</v>
+      </c>
+      <c r="H102">
+        <v>11</v>
+      </c>
+      <c r="I102">
+        <v>7</v>
+      </c>
+      <c r="J102">
+        <v>8</v>
+      </c>
+      <c r="K102">
+        <v>9.5</v>
+      </c>
+      <c r="L102">
+        <v>9.5</v>
+      </c>
+      <c r="M102" s="2">
+        <v>1</v>
+      </c>
+      <c r="N102" s="2">
+        <v>1.0802804776647501</v>
+      </c>
+      <c r="O102" s="2">
+        <v>1.214285714285714</v>
+      </c>
     </row>
     <row r="103" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
-        <v>160</v>
+        <v>73</v>
       </c>
       <c r="B103" t="s">
-        <v>21</v>
+        <v>66</v>
       </c>
       <c r="C103" t="s">
-        <v>19</v>
-      </c>
-      <c r="M103" s="2"/>
-      <c r="N103" s="2"/>
-      <c r="O103" s="2"/>
+        <v>57</v>
+      </c>
+      <c r="D103">
+        <v>25</v>
+      </c>
+      <c r="E103">
+        <v>6.5</v>
+      </c>
+      <c r="F103">
+        <v>7.5</v>
+      </c>
+      <c r="G103">
+        <v>9</v>
+      </c>
+      <c r="H103">
+        <v>9.5</v>
+      </c>
+      <c r="I103">
+        <v>6.5</v>
+      </c>
+      <c r="J103">
+        <v>7.5</v>
+      </c>
+      <c r="K103">
+        <v>8.5</v>
+      </c>
+      <c r="L103">
+        <v>9</v>
+      </c>
+      <c r="M103" s="2">
+        <v>0.94117647058823528</v>
+      </c>
+      <c r="N103" s="2">
+        <v>1.050012661064426</v>
+      </c>
+      <c r="O103" s="2">
+        <v>1.142857142857143</v>
+      </c>
     </row>
     <row r="104" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
-        <v>161</v>
+        <v>74</v>
       </c>
       <c r="B104" t="s">
-        <v>30</v>
+        <v>66</v>
       </c>
       <c r="C104" t="s">
-        <v>28</v>
-      </c>
-      <c r="M104" s="2"/>
-      <c r="N104" s="2"/>
-      <c r="O104" s="2"/>
+        <v>57</v>
+      </c>
+      <c r="D104">
+        <v>23</v>
+      </c>
+      <c r="E104">
+        <v>9</v>
+      </c>
+      <c r="F104">
+        <v>9</v>
+      </c>
+      <c r="G104">
+        <v>11</v>
+      </c>
+      <c r="H104">
+        <v>12</v>
+      </c>
+      <c r="I104">
+        <v>8.5</v>
+      </c>
+      <c r="J104">
+        <v>9</v>
+      </c>
+      <c r="K104">
+        <v>11</v>
+      </c>
+      <c r="L104">
+        <v>11</v>
+      </c>
+      <c r="M104" s="2">
+        <v>0.94736842105263153</v>
+      </c>
+      <c r="N104" s="2">
+        <v>1.031837163522487</v>
+      </c>
+      <c r="O104" s="2">
+        <v>1.2222222222222221</v>
+      </c>
     </row>
     <row r="105" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
-        <v>162</v>
+        <v>77</v>
       </c>
       <c r="B105" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="C105" t="s">
         <v>57</v>
@@ -3723,10 +3670,10 @@
     </row>
     <row r="106" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
-        <v>163</v>
+        <v>78</v>
       </c>
       <c r="B106" t="s">
-        <v>164</v>
+        <v>66</v>
       </c>
       <c r="C106" t="s">
         <v>57</v>
@@ -3737,10 +3684,10 @@
     </row>
     <row r="107" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
-        <v>165</v>
+        <v>79</v>
       </c>
       <c r="B107" t="s">
-        <v>164</v>
+        <v>66</v>
       </c>
       <c r="C107" t="s">
         <v>57</v>
@@ -3751,10 +3698,10 @@
     </row>
     <row r="108" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
-        <v>166</v>
+        <v>80</v>
       </c>
       <c r="B108" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="C108" t="s">
         <v>57</v>
@@ -3765,10 +3712,10 @@
     </row>
     <row r="109" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
-        <v>167</v>
+        <v>93</v>
       </c>
       <c r="B109" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="C109" t="s">
         <v>57</v>
@@ -3779,27 +3726,60 @@
     </row>
     <row r="110" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
-        <v>168</v>
+        <v>95</v>
       </c>
       <c r="B110" t="s">
-        <v>21</v>
+        <v>96</v>
       </c>
       <c r="C110" t="s">
-        <v>19</v>
-      </c>
-      <c r="M110" s="2"/>
-      <c r="N110" s="2"/>
-      <c r="O110" s="2"/>
+        <v>57</v>
+      </c>
+      <c r="D110">
+        <v>25</v>
+      </c>
+      <c r="E110">
+        <v>8</v>
+      </c>
+      <c r="F110">
+        <v>8</v>
+      </c>
+      <c r="G110">
+        <v>10</v>
+      </c>
+      <c r="H110">
+        <v>10</v>
+      </c>
+      <c r="I110">
+        <v>6</v>
+      </c>
+      <c r="J110">
+        <v>6</v>
+      </c>
+      <c r="K110">
+        <v>7.5</v>
+      </c>
+      <c r="L110">
+        <v>8</v>
+      </c>
+      <c r="M110" s="2">
+        <v>1.0666666666666671</v>
+      </c>
+      <c r="N110" s="2">
+        <v>1.2846247619047619</v>
+      </c>
+      <c r="O110" s="2">
+        <v>1.461538461538461</v>
+      </c>
     </row>
     <row r="111" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
-        <v>169</v>
+        <v>97</v>
       </c>
       <c r="B111" t="s">
-        <v>21</v>
+        <v>96</v>
       </c>
       <c r="C111" t="s">
-        <v>19</v>
+        <v>57</v>
       </c>
       <c r="M111" s="2"/>
       <c r="N111" s="2"/>
@@ -3807,13 +3787,13 @@
     </row>
     <row r="112" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
-        <v>170</v>
+        <v>98</v>
       </c>
       <c r="B112" t="s">
-        <v>43</v>
+        <v>96</v>
       </c>
       <c r="C112" t="s">
-        <v>28</v>
+        <v>57</v>
       </c>
       <c r="M112" s="2"/>
       <c r="N112" s="2"/>
@@ -3821,13 +3801,13 @@
     </row>
     <row r="113" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
-        <v>171</v>
+        <v>101</v>
       </c>
       <c r="B113" t="s">
-        <v>43</v>
+        <v>102</v>
       </c>
       <c r="C113" t="s">
-        <v>28</v>
+        <v>57</v>
       </c>
       <c r="M113" s="2"/>
       <c r="N113" s="2"/>
@@ -3835,13 +3815,13 @@
     </row>
     <row r="114" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
-        <v>172</v>
+        <v>103</v>
       </c>
       <c r="B114" t="s">
-        <v>45</v>
+        <v>102</v>
       </c>
       <c r="C114" t="s">
-        <v>28</v>
+        <v>57</v>
       </c>
       <c r="M114" s="2"/>
       <c r="N114" s="2"/>
@@ -3849,27 +3829,60 @@
     </row>
     <row r="115" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
-        <v>173</v>
+        <v>105</v>
       </c>
       <c r="B115" t="s">
-        <v>53</v>
+        <v>106</v>
       </c>
       <c r="C115" t="s">
-        <v>19</v>
-      </c>
-      <c r="M115" s="2"/>
-      <c r="N115" s="2"/>
-      <c r="O115" s="2"/>
+        <v>57</v>
+      </c>
+      <c r="D115">
+        <v>25</v>
+      </c>
+      <c r="E115">
+        <v>6.5</v>
+      </c>
+      <c r="F115">
+        <v>6.5</v>
+      </c>
+      <c r="G115">
+        <v>8</v>
+      </c>
+      <c r="H115">
+        <v>9.5</v>
+      </c>
+      <c r="I115">
+        <v>5</v>
+      </c>
+      <c r="J115">
+        <v>5.5</v>
+      </c>
+      <c r="K115">
+        <v>6.5</v>
+      </c>
+      <c r="L115">
+        <v>7</v>
+      </c>
+      <c r="M115" s="2">
+        <v>1</v>
+      </c>
+      <c r="N115" s="2">
+        <v>1.242687445887446</v>
+      </c>
+      <c r="O115" s="2">
+        <v>1.6</v>
+      </c>
     </row>
     <row r="116" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
-        <v>174</v>
+        <v>117</v>
       </c>
       <c r="B116" t="s">
-        <v>53</v>
+        <v>118</v>
       </c>
       <c r="C116" t="s">
-        <v>19</v>
+        <v>57</v>
       </c>
       <c r="M116" s="2"/>
       <c r="N116" s="2"/>
@@ -3877,13 +3890,13 @@
     </row>
     <row r="117" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
-        <v>175</v>
+        <v>121</v>
       </c>
       <c r="B117" t="s">
-        <v>53</v>
+        <v>118</v>
       </c>
       <c r="C117" t="s">
-        <v>19</v>
+        <v>57</v>
       </c>
       <c r="M117" s="2"/>
       <c r="N117" s="2"/>
@@ -3891,13 +3904,13 @@
     </row>
     <row r="118" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
-        <v>176</v>
+        <v>125</v>
       </c>
       <c r="B118" t="s">
-        <v>53</v>
+        <v>96</v>
       </c>
       <c r="C118" t="s">
-        <v>19</v>
+        <v>57</v>
       </c>
       <c r="M118" s="2"/>
       <c r="N118" s="2"/>
@@ -3905,13 +3918,13 @@
     </row>
     <row r="119" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
-        <v>177</v>
+        <v>126</v>
       </c>
       <c r="B119" t="s">
-        <v>53</v>
+        <v>118</v>
       </c>
       <c r="C119" t="s">
-        <v>19</v>
+        <v>57</v>
       </c>
       <c r="M119" s="2"/>
       <c r="N119" s="2"/>
@@ -3919,13 +3932,13 @@
     </row>
     <row r="120" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
-        <v>178</v>
+        <v>127</v>
       </c>
       <c r="B120" t="s">
-        <v>53</v>
+        <v>118</v>
       </c>
       <c r="C120" t="s">
-        <v>19</v>
+        <v>57</v>
       </c>
       <c r="M120" s="2"/>
       <c r="N120" s="2"/>
@@ -3933,10 +3946,10 @@
     </row>
     <row r="121" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
-        <v>179</v>
+        <v>131</v>
       </c>
       <c r="B121" t="s">
-        <v>66</v>
+        <v>118</v>
       </c>
       <c r="C121" t="s">
         <v>57</v>
@@ -3947,13 +3960,13 @@
     </row>
     <row r="122" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
-        <v>180</v>
+        <v>132</v>
       </c>
       <c r="B122" t="s">
-        <v>85</v>
+        <v>118</v>
       </c>
       <c r="C122" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="M122" s="2"/>
       <c r="N122" s="2"/>
@@ -3961,13 +3974,13 @@
     </row>
     <row r="123" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
-        <v>181</v>
+        <v>133</v>
       </c>
       <c r="B123" t="s">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="C123" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="M123" s="2"/>
       <c r="N123" s="2"/>
@@ -3975,13 +3988,13 @@
     </row>
     <row r="124" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
-        <v>182</v>
+        <v>137</v>
       </c>
       <c r="B124" t="s">
-        <v>85</v>
+        <v>118</v>
       </c>
       <c r="C124" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="M124" s="2"/>
       <c r="N124" s="2"/>
@@ -3989,13 +4002,13 @@
     </row>
     <row r="125" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
-        <v>183</v>
+        <v>138</v>
       </c>
       <c r="B125" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="C125" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="M125" s="2"/>
       <c r="N125" s="2"/>
@@ -4003,10 +4016,10 @@
     </row>
     <row r="126" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
-        <v>184</v>
+        <v>139</v>
       </c>
       <c r="B126" t="s">
-        <v>96</v>
+        <v>118</v>
       </c>
       <c r="C126" t="s">
         <v>57</v>
@@ -4017,10 +4030,10 @@
     </row>
     <row r="127" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
-        <v>185</v>
+        <v>145</v>
       </c>
       <c r="B127" t="s">
-        <v>96</v>
+        <v>146</v>
       </c>
       <c r="C127" t="s">
         <v>57</v>
@@ -4031,10 +4044,10 @@
     </row>
     <row r="128" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
-        <v>186</v>
+        <v>147</v>
       </c>
       <c r="B128" t="s">
-        <v>96</v>
+        <v>118</v>
       </c>
       <c r="C128" t="s">
         <v>57</v>
@@ -4045,10 +4058,10 @@
     </row>
     <row r="129" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
-        <v>187</v>
+        <v>151</v>
       </c>
       <c r="B129" t="s">
-        <v>96</v>
+        <v>71</v>
       </c>
       <c r="C129" t="s">
         <v>57</v>
@@ -4059,10 +4072,10 @@
     </row>
     <row r="130" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
-        <v>188</v>
+        <v>159</v>
       </c>
       <c r="B130" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="C130" t="s">
         <v>57</v>
@@ -4073,10 +4086,10 @@
     </row>
     <row r="131" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
-        <v>189</v>
+        <v>162</v>
       </c>
       <c r="B131" t="s">
-        <v>96</v>
+        <v>59</v>
       </c>
       <c r="C131" t="s">
         <v>57</v>
@@ -4087,10 +4100,10 @@
     </row>
     <row r="132" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
-        <v>190</v>
+        <v>163</v>
       </c>
       <c r="B132" t="s">
-        <v>96</v>
+        <v>164</v>
       </c>
       <c r="C132" t="s">
         <v>57</v>
@@ -4101,13 +4114,13 @@
     </row>
     <row r="133" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
-        <v>191</v>
+        <v>165</v>
       </c>
       <c r="B133" t="s">
-        <v>108</v>
+        <v>164</v>
       </c>
       <c r="C133" t="s">
-        <v>109</v>
+        <v>57</v>
       </c>
       <c r="M133" s="2"/>
       <c r="N133" s="2"/>
@@ -4115,13 +4128,13 @@
     </row>
     <row r="134" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
-        <v>192</v>
+        <v>166</v>
       </c>
       <c r="B134" t="s">
-        <v>91</v>
+        <v>59</v>
       </c>
       <c r="C134" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="M134" s="2"/>
       <c r="N134" s="2"/>
@@ -4129,13 +4142,13 @@
     </row>
     <row r="135" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A135" t="s">
-        <v>193</v>
+        <v>167</v>
       </c>
       <c r="B135" t="s">
-        <v>115</v>
+        <v>66</v>
       </c>
       <c r="C135" t="s">
-        <v>28</v>
+        <v>57</v>
       </c>
       <c r="M135" s="2"/>
       <c r="N135" s="2"/>
@@ -4143,13 +4156,13 @@
     </row>
     <row r="136" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A136" t="s">
-        <v>194</v>
+        <v>179</v>
       </c>
       <c r="B136" t="s">
-        <v>43</v>
+        <v>66</v>
       </c>
       <c r="C136" t="s">
-        <v>28</v>
+        <v>57</v>
       </c>
       <c r="M136" s="2"/>
       <c r="N136" s="2"/>
@@ -4157,13 +4170,13 @@
     </row>
     <row r="137" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A137" t="s">
-        <v>195</v>
+        <v>184</v>
       </c>
       <c r="B137" t="s">
-        <v>71</v>
+        <v>96</v>
       </c>
       <c r="C137" t="s">
-        <v>72</v>
+        <v>57</v>
       </c>
       <c r="M137" s="2"/>
       <c r="N137" s="2"/>
@@ -4171,13 +4184,13 @@
     </row>
     <row r="138" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A138" t="s">
-        <v>196</v>
+        <v>185</v>
       </c>
       <c r="B138" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="C138" t="s">
-        <v>28</v>
+        <v>57</v>
       </c>
       <c r="M138" s="2"/>
       <c r="N138" s="2"/>
@@ -4185,13 +4198,13 @@
     </row>
     <row r="139" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A139" t="s">
-        <v>197</v>
+        <v>186</v>
       </c>
       <c r="B139" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="C139" t="s">
-        <v>28</v>
+        <v>57</v>
       </c>
       <c r="M139" s="2"/>
       <c r="N139" s="2"/>
@@ -4199,13 +4212,13 @@
     </row>
     <row r="140" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A140" t="s">
-        <v>198</v>
+        <v>187</v>
       </c>
       <c r="B140" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="C140" t="s">
-        <v>28</v>
+        <v>57</v>
       </c>
       <c r="M140" s="2"/>
       <c r="N140" s="2"/>
@@ -4213,13 +4226,13 @@
     </row>
     <row r="141" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A141" t="s">
-        <v>199</v>
+        <v>188</v>
       </c>
       <c r="B141" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="C141" t="s">
-        <v>28</v>
+        <v>57</v>
       </c>
       <c r="M141" s="2"/>
       <c r="N141" s="2"/>
@@ -4227,13 +4240,13 @@
     </row>
     <row r="142" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A142" t="s">
-        <v>200</v>
+        <v>189</v>
       </c>
       <c r="B142" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="C142" t="s">
-        <v>28</v>
+        <v>57</v>
       </c>
       <c r="M142" s="2"/>
       <c r="N142" s="2"/>
@@ -4241,13 +4254,13 @@
     </row>
     <row r="143" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A143" t="s">
-        <v>201</v>
+        <v>190</v>
       </c>
       <c r="B143" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="C143" t="s">
-        <v>28</v>
+        <v>57</v>
       </c>
       <c r="M143" s="2"/>
       <c r="N143" s="2"/>
@@ -4267,6 +4280,9 @@
       </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Q145">
+    <sortCondition ref="C2:C145"/>
+  </sortState>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
